--- a/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>674598</t>
+          <t>672639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>735003</t>
+          <t>736161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1032201</t>
+          <t>1032373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1090017</t>
+          <t>1086684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1724960</t>
+          <t>1726641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1810784</t>
+          <t>1808969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296720</t>
+          <t>295562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>357125</t>
+          <t>359084</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225096</t>
+          <t>228429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282912</t>
+          <t>282740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>536051</t>
+          <t>537866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>621875</t>
+          <t>620194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>612629</t>
+          <t>614636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>695907</t>
+          <t>693508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>801185</t>
+          <t>806941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>881829</t>
+          <t>885106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1435019</t>
+          <t>1443198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1551054</t>
+          <t>1555069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997506</t>
+          <t>999905</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1080784</t>
+          <t>1078777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705844</t>
+          <t>702567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>786488</t>
+          <t>780732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1730032</t>
+          <t>1726017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1846067</t>
+          <t>1837888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195629</t>
+          <t>194979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243273</t>
+          <t>244399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>227649</t>
+          <t>228955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272003</t>
+          <t>272593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>436523</t>
+          <t>436403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>503557</t>
+          <t>501265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308135</t>
+          <t>307009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>355779</t>
+          <t>356429</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204409</t>
+          <t>203819</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248763</t>
+          <t>247457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>524263</t>
+          <t>526555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>591297</t>
+          <t>591417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1519872</t>
+          <t>1520616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1638673</t>
+          <t>1636835</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2100896</t>
+          <t>2105314</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2222608</t>
+          <t>2214989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3652324</t>
+          <t>3655098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3821214</t>
+          <t>3821684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1637870</t>
+          <t>1639708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1756671</t>
+          <t>1755927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1156589</t>
+          <t>1164208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1278301</t>
+          <t>1273883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2834527</t>
+          <t>2834057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3003417</t>
+          <t>3000643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>720714</t>
+          <t>721279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>776282</t>
+          <t>774146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1139752</t>
+          <t>1140014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1189559</t>
+          <t>1193060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1878892</t>
+          <t>1878986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1952856</t>
+          <t>1950968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198361</t>
+          <t>200497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253929</t>
+          <t>253364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148238</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198045</t>
+          <t>197783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>359584</t>
+          <t>361472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>433548</t>
+          <t>433454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>881946</t>
+          <t>871317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>972143</t>
+          <t>967589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1001041</t>
+          <t>1003636</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1084272</t>
+          <t>1085979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1905296</t>
+          <t>1908929</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2026697</t>
+          <t>2028170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>991814</t>
+          <t>996368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1082011</t>
+          <t>1092640</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>673531</t>
+          <t>671824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>756762</t>
+          <t>754167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1695063</t>
+          <t>1693590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1816464</t>
+          <t>1812831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>206797</t>
+          <t>203422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>254504</t>
+          <t>252453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>226430</t>
+          <t>226631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271411</t>
+          <t>270414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>443065</t>
+          <t>447118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>510119</t>
+          <t>508677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226677</t>
+          <t>228728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>274384</t>
+          <t>277759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187220</t>
+          <t>188217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232201</t>
+          <t>232000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>429694</t>
+          <t>431136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>496748</t>
+          <t>492695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,42%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1838857</t>
+          <t>1846473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1958098</t>
+          <t>1965979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2400426</t>
+          <t>2405444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2509820</t>
+          <t>2513092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4279163</t>
+          <t>4278122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4442682</t>
+          <t>4439875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1461684</t>
+          <t>1453803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1580925</t>
+          <t>1573309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1044410</t>
+          <t>1041138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1153804</t>
+          <t>1148786</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2531330</t>
+          <t>2534137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2694849</t>
+          <t>2695890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>526578</t>
+          <t>527089</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>573696</t>
+          <t>574525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>834131</t>
+          <t>830882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>876524</t>
+          <t>877488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1374830</t>
+          <t>1378336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1440002</t>
+          <t>1442960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>180651</t>
+          <t>179822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>227769</t>
+          <t>227258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118136</t>
+          <t>117172</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160529</t>
+          <t>163778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>309005</t>
+          <t>306047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374177</t>
+          <t>370671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>948986</t>
+          <t>946447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1040134</t>
+          <t>1041298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1089181</t>
+          <t>1085609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1174234</t>
+          <t>1175082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2055484</t>
+          <t>2057925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2189397</t>
+          <t>2189670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1036251</t>
+          <t>1035087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1127399</t>
+          <t>1129938</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>814066</t>
+          <t>813218</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>899119</t>
+          <t>902691</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1875288</t>
+          <t>1875015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2009201</t>
+          <t>2006760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>197841</t>
+          <t>199960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244243</t>
+          <t>247993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240414</t>
+          <t>240360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>287675</t>
+          <t>288570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>454589</t>
+          <t>456239</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>519956</t>
+          <t>520849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302643</t>
+          <t>298893</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>349045</t>
+          <t>346926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261465</t>
+          <t>260570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>308726</t>
+          <t>308780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576071</t>
+          <t>575178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641438</t>
+          <t>639788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1708306</t>
+          <t>1708287</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1826709</t>
+          <t>1825091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2196674</t>
+          <t>2192331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2313531</t>
+          <t>2309669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3935176</t>
+          <t>3941042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4102585</t>
+          <t>4103010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1550909</t>
+          <t>1552527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1669312</t>
+          <t>1669331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1218569</t>
+          <t>1222431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1335426</t>
+          <t>1339769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2807133</t>
+          <t>2806708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2974542</t>
+          <t>2968676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>302522</t>
+          <t>300866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>343714</t>
+          <t>342292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>513968</t>
+          <t>513350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>553175</t>
+          <t>552186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>828621</t>
+          <t>831568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>887127</t>
+          <t>889887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171224</t>
+          <t>172646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>212416</t>
+          <t>214072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202333</t>
+          <t>203322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241540</t>
+          <t>242158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>383319</t>
+          <t>380559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441825</t>
+          <t>438878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>540707</t>
+          <t>528883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>888741</t>
+          <t>886903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>855221</t>
+          <t>857418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1349720</t>
+          <t>1308354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1548644</t>
+          <t>1510795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2170077</t>
+          <t>2144760</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1401586</t>
+          <t>1403424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1749620</t>
+          <t>1761444</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>888103</t>
+          <t>929469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1382602</t>
+          <t>1380405</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2358073</t>
+          <t>2383390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2979506</t>
+          <t>3017355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>189530</t>
+          <t>188410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241274</t>
+          <t>242143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210882</t>
+          <t>211760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254233</t>
+          <t>255000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>415151</t>
+          <t>414016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>480181</t>
+          <t>481227</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405349</t>
+          <t>404480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457093</t>
+          <t>458213</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>406230</t>
+          <t>405463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449581</t>
+          <t>448703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>826905</t>
+          <t>825859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>891935</t>
+          <t>893070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1005639</t>
+          <t>1032625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1443088</t>
+          <t>1439462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1626972</t>
+          <t>1628759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2118701</t>
+          <t>2143139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2784440</t>
+          <t>2783964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3451212</t>
+          <t>3415469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2008801</t>
+          <t>2012427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2446250</t>
+          <t>2419264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1535093</t>
+          <t>1510655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2026822</t>
+          <t>2025035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3654471</t>
+          <t>3690214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4321243</t>
+          <t>4321719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>672639</t>
+          <t>675933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>736161</t>
+          <t>733782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1032373</t>
+          <t>1032605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1086684</t>
+          <t>1090816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1726641</t>
+          <t>1724435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1808969</t>
+          <t>1810431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295562</t>
+          <t>297941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359084</t>
+          <t>355790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228429</t>
+          <t>224297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282740</t>
+          <t>282508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537866</t>
+          <t>536404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>620194</t>
+          <t>622400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>614636</t>
+          <t>613515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>693508</t>
+          <t>695593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>806941</t>
+          <t>803574</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>885106</t>
+          <t>882485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1443198</t>
+          <t>1434097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1555069</t>
+          <t>1552441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999905</t>
+          <t>997820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1078777</t>
+          <t>1079898</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>702567</t>
+          <t>705188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>780732</t>
+          <t>784099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1726017</t>
+          <t>1728645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1837888</t>
+          <t>1846989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194979</t>
+          <t>195480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244399</t>
+          <t>243350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>228955</t>
+          <t>224195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272593</t>
+          <t>270543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>436403</t>
+          <t>433342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>501265</t>
+          <t>500243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307009</t>
+          <t>308058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>356429</t>
+          <t>355928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>203819</t>
+          <t>205869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247457</t>
+          <t>252217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>526555</t>
+          <t>527577</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>591417</t>
+          <t>594478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1520616</t>
+          <t>1523547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1636835</t>
+          <t>1639290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2105314</t>
+          <t>2098769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2214989</t>
+          <t>2211245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3655098</t>
+          <t>3649928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3821684</t>
+          <t>3815091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1639708</t>
+          <t>1637253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1755927</t>
+          <t>1752996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1164208</t>
+          <t>1167952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1273883</t>
+          <t>1280428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2834057</t>
+          <t>2840650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3000643</t>
+          <t>3005813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>721279</t>
+          <t>724095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>774146</t>
+          <t>774300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1140014</t>
+          <t>1141669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1193060</t>
+          <t>1191425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1878986</t>
+          <t>1878839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1950968</t>
+          <t>1953188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,46%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200497</t>
+          <t>200343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253364</t>
+          <t>250548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144737</t>
+          <t>146372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197783</t>
+          <t>196128</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>359252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>433454</t>
+          <t>433601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>871317</t>
+          <t>881174</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>967589</t>
+          <t>970629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1003636</t>
+          <t>1003774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1085979</t>
+          <t>1087819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1908929</t>
+          <t>1901469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2028170</t>
+          <t>2024392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996368</t>
+          <t>993328</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1092640</t>
+          <t>1082783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>671824</t>
+          <t>669984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>754167</t>
+          <t>754029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1693590</t>
+          <t>1697368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1812831</t>
+          <t>1820291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203422</t>
+          <t>205795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>252453</t>
+          <t>252794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>226631</t>
+          <t>224038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>270414</t>
+          <t>270595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>447118</t>
+          <t>449535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>508677</t>
+          <t>511145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228728</t>
+          <t>228387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277759</t>
+          <t>275386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188217</t>
+          <t>188036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232000</t>
+          <t>234593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>431136</t>
+          <t>428668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>492695</t>
+          <t>490278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1846473</t>
+          <t>1844369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1965979</t>
+          <t>1962355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2405444</t>
+          <t>2399140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2513092</t>
+          <t>2515721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4278122</t>
+          <t>4271366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4439875</t>
+          <t>4440036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1453803</t>
+          <t>1457427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1573309</t>
+          <t>1575413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1041138</t>
+          <t>1038509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1148786</t>
+          <t>1155090</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2534137</t>
+          <t>2533976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2695890</t>
+          <t>2702646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>527089</t>
+          <t>526790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>574525</t>
+          <t>574833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>830882</t>
+          <t>836854</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>877488</t>
+          <t>877595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1378336</t>
+          <t>1372211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1442960</t>
+          <t>1440187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>179822</t>
+          <t>179514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>227258</t>
+          <t>227557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117172</t>
+          <t>117065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163778</t>
+          <t>157806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306047</t>
+          <t>308820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>370671</t>
+          <t>376796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>946447</t>
+          <t>951141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1041298</t>
+          <t>1042091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1085609</t>
+          <t>1088161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1175082</t>
+          <t>1177220</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2057925</t>
+          <t>2055086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2189670</t>
+          <t>2187455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1035087</t>
+          <t>1034294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1129938</t>
+          <t>1125244</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>813218</t>
+          <t>811080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>902691</t>
+          <t>900139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1875015</t>
+          <t>1877230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2006760</t>
+          <t>2009599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>199960</t>
+          <t>200033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>247993</t>
+          <t>247353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240360</t>
+          <t>242462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>288570</t>
+          <t>289110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>456239</t>
+          <t>454533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>520849</t>
+          <t>523741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298893</t>
+          <t>299533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346926</t>
+          <t>346853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260570</t>
+          <t>260030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>308780</t>
+          <t>306678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575178</t>
+          <t>572286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639788</t>
+          <t>641494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1708287</t>
+          <t>1708050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1825091</t>
+          <t>1822984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2192331</t>
+          <t>2193422</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2309669</t>
+          <t>2316451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3941042</t>
+          <t>3939676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4103010</t>
+          <t>4101987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1552527</t>
+          <t>1554634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1669331</t>
+          <t>1669568</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1222431</t>
+          <t>1215649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1339769</t>
+          <t>1338678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2806708</t>
+          <t>2807731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2968676</t>
+          <t>2970042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>323514</t>
+          <t>340822</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>300866</t>
+          <t>316096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>342292</t>
+          <t>364800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>534791</t>
+          <t>575451</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>513350</t>
+          <t>553527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>552186</t>
+          <t>596771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>858305</t>
+          <t>916273</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>831568</t>
+          <t>884119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>889887</t>
+          <t>950731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>191424</t>
+          <t>237707</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172646</t>
+          <t>213729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214072</t>
+          <t>262433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>220717</t>
+          <t>246587</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203322</t>
+          <t>225267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242158</t>
+          <t>268511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>412141</t>
+          <t>484294</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>380559</t>
+          <t>449836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>438878</t>
+          <t>516448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>778251</t>
+          <t>822434</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>528883</t>
+          <t>776031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>886903</t>
+          <t>874903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1008486</t>
+          <t>892405</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>857418</t>
+          <t>852676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1308354</t>
+          <t>938616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1786737</t>
+          <t>1714839</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1510795</t>
+          <t>1644131</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2144760</t>
+          <t>1782485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1512076</t>
+          <t>1408132</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1403424</t>
+          <t>1355663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1761444</t>
+          <t>1454535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1229337</t>
+          <t>1278987</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>929469</t>
+          <t>1232776</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1380405</t>
+          <t>1318716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2741413</t>
+          <t>2687120</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2383390</t>
+          <t>2619474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3017355</t>
+          <t>2757828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>215109</t>
+          <t>232604</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188410</t>
+          <t>207906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242143</t>
+          <t>260591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>232462</t>
+          <t>257703</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211760</t>
+          <t>234856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255000</t>
+          <t>279988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>447571</t>
+          <t>490307</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>414016</t>
+          <t>453131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>481227</t>
+          <t>523410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>431514</t>
+          <t>478983</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>404480</t>
+          <t>450996</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>458213</t>
+          <t>503681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>428001</t>
+          <t>477174</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>405463</t>
+          <t>454889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448703</t>
+          <t>500021</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>859515</t>
+          <t>956157</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>825859</t>
+          <t>923054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>893070</t>
+          <t>993333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1316875</t>
+          <t>1395860</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1032625</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1439462</t>
+          <t>1455377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1775739</t>
+          <t>1725559</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1628759</t>
+          <t>1670900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2143139</t>
+          <t>1777207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3092614</t>
+          <t>3121419</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2783964</t>
+          <t>3034307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3415469</t>
+          <t>3198032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2135014</t>
+          <t>2124823</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2012427</t>
+          <t>2065306</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2419264</t>
+          <t>2190672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1878055</t>
+          <t>2002748</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1510655</t>
+          <t>1951100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2025035</t>
+          <t>2057407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4013069</t>
+          <t>4127571</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3690214</t>
+          <t>4050958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4321719</t>
+          <t>4214683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
